--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_equip_suit.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_equip_suit.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_equip_suit" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="219">
   <si>
     <t>id</t>
   </si>
@@ -167,7 +167,7 @@
     <t>21000013#21541#2530#2531#2532#21000015#21542#25302#25312#25322</t>
   </si>
   <si>
-    <t>2#320011#15|3#209011#50|4#202052#500|5#207011#50&amp;1031#30&amp;305012#1000&amp;303012#1000</t>
+    <t>2#320011#15|3#209011#50|4#320013#500|5#207011#50&amp;1031#30&amp;305012#1000&amp;303012#1000</t>
   </si>
   <si>
     <t>4</t>
@@ -209,7 +209,7 @@
     <t>20410241#20810241#20410261#20810261</t>
   </si>
   <si>
-    <t>2#305012#2000&amp;305031#50</t>
+    <t>2#305012#2000&amp;305072#50</t>
   </si>
   <si>
     <t>菲斯特的强化白金套</t>
@@ -236,7 +236,7 @@
     <t>20610231#20710231#20810231#20910231#21000023#20610251#20710251#20810251#20910251#21000025</t>
   </si>
   <si>
-    <t>2#1031#30|3#304012#500|4#10003#15|5#207011#50&amp;320011#25&amp;202052#1500</t>
+    <t>2#1031#30|3#304012#500|4#10003#15|5#207011#50&amp;320011#25&amp;320013#1500</t>
   </si>
   <si>
     <t>菲斯特的白金套</t>
@@ -245,7 +245,7 @@
     <t>20610331#20710331#20910331#21100023#21100053#20610351#20710351#20910351#21100026#21100055</t>
   </si>
   <si>
-    <t>2#10003#15|3#10004#30|4#202052#1000|5#10001#15&amp;320011#25&amp;303012#1000&amp;303031#20</t>
+    <t>2#10003#15|3#10004#30|4#320013#1000|5#10001#15&amp;320011#25&amp;303012#1000&amp;303072#20</t>
   </si>
   <si>
     <t>汉斯的龙王套</t>
@@ -254,7 +254,7 @@
     <t>20310431#20410431#20710431#20910431#20310451#20410451#20710451#20910451</t>
   </si>
   <si>
-    <t>2#206011#25|3#304012#1000|4#320011#20&amp;303012#1500&amp;305012#1500&amp;303031#20&amp;305031#20</t>
+    <t>2#206011#25|3#304012#1000|4#320011#20&amp;303012#1500&amp;305012#1500&amp;303072#20&amp;305072#20</t>
   </si>
   <si>
     <t>安东尼斯的魔王套</t>
@@ -272,7 +272,7 @@
     <t>20420131#20620131#20720131#20820131#21000033#21100063#21111#20420151#20620151#20720151#20820151#21000035#21100066#21112</t>
   </si>
   <si>
-    <t>2#10003#10|3#202052#500|4#320011#10|5#208011#30|6#207011#30|7#1031#20&amp;303012#1000&amp;305012#1000&amp;10003#30</t>
+    <t>2#10003#10|3#320013#500|4#320011#10|5#208011#30|6#207011#30|7#1031#20&amp;303012#1000&amp;305012#1000&amp;10003#30</t>
   </si>
   <si>
     <t>奥维兰的强化革套</t>
@@ -281,7 +281,7 @@
     <t>20420141#20820141#20920141#20420161#20820161#20920161</t>
   </si>
   <si>
-    <t>2#202052#1000|3#10003#20&amp;208011#100&amp;320011#30</t>
+    <t>2#320013#1000|3#10003#20&amp;208011#100&amp;320011#30</t>
   </si>
   <si>
     <t>索尔思的骷髅套</t>
@@ -290,7 +290,7 @@
     <t>20620231#20820231#20920231#21000043#20620251#20820251#20920251#21000045</t>
   </si>
   <si>
-    <t>2#320011#15|3#10004#20|4#202052#1000&amp;304012#500&amp;209011#50&amp;1031#5</t>
+    <t>2#320011#15|3#10004#20|4#320013#1000&amp;304012#500&amp;209011#50&amp;1031#5</t>
   </si>
   <si>
     <t>索尔思的强化骷髅套</t>
@@ -317,7 +317,7 @@
     <t>20420431#20620431#20720431#21100033#20420451#20620451#20720451#21100035</t>
   </si>
   <si>
-    <t>2#304012#1000|3#208011#50|4#202052#1000&amp;303012#1500&amp;305012#1500&amp;303031#20&amp;305031#20</t>
+    <t>2#304012#1000|3#208011#50|4#320013#1000&amp;303012#1500&amp;305012#1500&amp;303072#20&amp;305072#20</t>
   </si>
   <si>
     <t>帕希的强化传说套</t>
@@ -326,7 +326,7 @@
     <t>20420441#20620441#20820441#20920441#20420461#20620461#20820461#20920461</t>
   </si>
   <si>
-    <t>2#320011#10|3#304012#1000|4#10003#30&amp;202052#1000&amp;317012#500</t>
+    <t>2#320011#10|3#304012#1000|4#10003#30&amp;320013#1000&amp;317012#500</t>
   </si>
   <si>
     <t>凯文的亚特兰蒂斯套</t>
@@ -335,7 +335,7 @@
     <t>21000053#2064010431#2084010431#2094010431#21000055#2064010451#2084010451#2094010451</t>
   </si>
   <si>
-    <t>2#317012#500|3#304012#1500|4#320011#15&amp;303012#1500&amp;303031#30&amp;202052#1000&amp;10001#30</t>
+    <t>2#317012#500|3#304012#1500|4#320011#15&amp;303012#1500&amp;303072#30&amp;320013#1000&amp;10001#30</t>
   </si>
   <si>
     <t>凯文的强化亚特兰蒂斯套</t>
@@ -344,7 +344,7 @@
     <t>21100034#2064010441#2084010441#2074010441#21100036#2064010461#2084010461#2074010461</t>
   </si>
   <si>
-    <t>2#320011#10|3#202052#1000|4#304012#1000&amp;303012#1500&amp;305012#1500&amp;206011#25&amp;600011#2000</t>
+    <t>2#320011#10|3#320013#1000|4#304012#1000&amp;303012#1500&amp;305012#1500&amp;206011#25&amp;600011#2000</t>
   </si>
   <si>
     <t>希尔芙的藤套</t>
@@ -416,7 +416,7 @@
     <t>20130431#20630431#20730431#20930431#21000063#20130451#20630451#20730451#20930451#21000065</t>
   </si>
   <si>
-    <t>2#10002#30|3#200011#20|4#206011#20|5#200021#20&amp;303012#1500&amp;305012#1500&amp;303031#20&amp;305031#20</t>
+    <t>2#10002#30|3#200011#20|4#206011#20|5#200021#20&amp;303012#1500&amp;305012#1500&amp;303072#20&amp;305072#20</t>
   </si>
   <si>
     <t>安吉拉的强化女神套</t>
@@ -434,7 +434,7 @@
     <t>21100064#20460431#20860431#20760431#21100065#20460451#20860451#20760451</t>
   </si>
   <si>
-    <t>2#304012#2000|3#206011#60|4#320011#30&amp;303012#1500&amp;305012#1500&amp;303031#20&amp;305031#20</t>
+    <t>2#304012#2000|3#206011#60|4#320011#30&amp;303012#1500&amp;305012#1500&amp;303072#20&amp;305072#20</t>
   </si>
   <si>
     <t>露西的强化红翼套</t>
@@ -443,7 +443,7 @@
     <t>20460441#20660441#20760441#20960441#20460461#20660461#20760461#20960461</t>
   </si>
   <si>
-    <t>2#202052#1500|3#320011#25|4#10003#30&amp;303012#1500&amp;305012#1500&amp;317012#500</t>
+    <t>2#320013#1500|3#320011#25|4#10003#30&amp;303012#1500&amp;305012#1500&amp;317012#500</t>
   </si>
   <si>
     <t>阿莱斯的圣魂套</t>
@@ -452,7 +452,7 @@
     <t>21100024#2085010631#2065010631#2045010631#21100025#2085010651#2065010651#2045010651</t>
   </si>
   <si>
-    <t>2#304012#1000|3#206011#40|4#320011#20&amp;303012#1500&amp;305012#1500&amp;303031#20&amp;305031#20</t>
+    <t>2#304012#1000|3#206011#40|4#320011#20&amp;303012#1500&amp;305012#1500&amp;303072#20&amp;305072#20</t>
   </si>
   <si>
     <t>阿莱斯的强化圣魂套</t>
@@ -578,7 +578,7 @@
     <t>20470351#20670351#20870351#20770351#20970351#20670631#20470631#20870631#20770631#20970631</t>
   </si>
   <si>
-    <t>2#207011#50|3#206011#40|4#304012#1500||5#317012#500&amp;303012#1500&amp;305012#1500&amp;303031#2000&amp;305031#2000</t>
+    <t>2#207011#50|3#206011#40|4#304012#1500||5#317012#500&amp;303012#1500&amp;305012#1500&amp;303072#20&amp;305072#20</t>
   </si>
   <si>
     <t>密诺瓦的圣职者套</t>
@@ -590,7 +590,7 @@
     <t>20770531#20470531#20670531#20870531#20970531#20470251#20670251#20870251#20770251#20970251</t>
   </si>
   <si>
-    <t>2#207011#30|3#320011#25|4#206011#20|5#304012#1000&amp;303012#1000&amp;305012#1000&amp;303031#1000&amp;305031#1000</t>
+    <t>2#207011#30|3#320011#25|4#206011#20|5#304012#1000&amp;303012#1000&amp;305012#1000&amp;303072#10&amp;305072#10</t>
   </si>
   <si>
     <t>海姆达尔的闪光套</t>
@@ -602,9 +602,6 @@
     <t>20670131#20870131#20770131#20970131#20670231#20870231#20770231#20970231</t>
   </si>
   <si>
-    <t>2#304012#2000|3#206011#60|4#320011#30&amp;303012#1500&amp;305012#1500&amp;303031#2000&amp;305031#2000</t>
-  </si>
-  <si>
     <t>卓越的玛古斯之魔焰套</t>
   </si>
   <si>
@@ -614,7 +611,7 @@
     <t>20770331#20870331#20670331#20470331#20770431#20870431#20670431#20470431</t>
   </si>
   <si>
-    <t>2#202052#1500|3#304012#1000|4#10003#30&amp;207011#50&amp;303012#1500&amp;305012#1500&amp;317012#500</t>
+    <t>2#320013#1500|3#304012#1000|4#10003#30&amp;207011#50&amp;303012#1500&amp;305012#1500&amp;317012#500</t>
   </si>
   <si>
     <t>卓越的巴德尔之魔焰套</t>
@@ -647,7 +644,7 @@
     <t>21200101#21200111</t>
   </si>
   <si>
-    <t>2#317012#100&amp;303012#400</t>
+    <t>2#317012#100&amp;303012#500</t>
   </si>
   <si>
     <t>二代耳环</t>
@@ -656,7 +653,7 @@
     <t>21200201#21200211</t>
   </si>
   <si>
-    <t>2#317012#200&amp;303012#800</t>
+    <t>2#317012#200&amp;303012#1000</t>
   </si>
   <si>
     <t>三代耳环</t>
@@ -665,7 +662,7 @@
     <t>21200301#21200311</t>
   </si>
   <si>
-    <t>2#317012#500&amp;303012#1200</t>
+    <t>2#317012#500&amp;303012#2000</t>
   </si>
   <si>
     <t>生命值</t>
@@ -4191,7 +4188,7 @@
         <v>2</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>187</v>
+        <v>131</v>
       </c>
       <c r="I79" s="6"/>
     </row>
@@ -4200,7 +4197,7 @@
         <v>76</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C80" s="6">
         <v>0</v>
@@ -4218,7 +4215,7 @@
         <v>2</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>187</v>
+        <v>131</v>
       </c>
       <c r="I80" s="6"/>
     </row>
@@ -4227,7 +4224,7 @@
         <v>77</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C81" s="6">
         <v>0</v>
@@ -4236,7 +4233,7 @@
         <v>39</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F81" s="6">
         <v>8</v>
@@ -4245,7 +4242,7 @@
         <v>2</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I81" s="6"/>
     </row>
@@ -4254,7 +4251,7 @@
         <v>78</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C82" s="6">
         <v>0</v>
@@ -4263,7 +4260,7 @@
         <v>39</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F82" s="6">
         <v>8</v>
@@ -4272,7 +4269,7 @@
         <v>2</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I82" s="6"/>
     </row>
@@ -4281,7 +4278,7 @@
         <v>666</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>32</v>
@@ -4290,7 +4287,7 @@
         <v>666</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F83" s="6" t="s">
         <v>47</v>
@@ -4299,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I83" s="6"/>
     </row>
@@ -4308,7 +4305,7 @@
         <v>777</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>32</v>
@@ -4317,7 +4314,7 @@
         <v>777</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>47</v>
@@ -4326,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I84" s="6"/>
     </row>
@@ -4335,7 +4332,7 @@
         <v>888</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>32</v>
@@ -4344,7 +4341,7 @@
         <v>888</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F85" s="6" t="s">
         <v>47</v>
@@ -4353,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I85" s="6"/>
     </row>
@@ -4362,7 +4359,7 @@
         <v>1001</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C86" s="6">
         <v>0</v>
@@ -4371,7 +4368,7 @@
         <v>1001</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F86" s="6">
         <v>2</v>
@@ -4380,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I86" s="13"/>
     </row>
@@ -4389,7 +4386,7 @@
         <v>1002</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C87" s="6">
         <v>0</v>
@@ -4398,7 +4395,7 @@
         <v>1002</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F87" s="6">
         <v>2</v>
@@ -4407,7 +4404,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I87" s="13"/>
     </row>
@@ -4416,7 +4413,7 @@
         <v>1003</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C88" s="6">
         <v>0</v>
@@ -4425,7 +4422,7 @@
         <v>1003</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F88" s="6">
         <v>2</v>
@@ -4434,7 +4431,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I88" s="13"/>
     </row>
@@ -4763,7 +4760,7 @@
         <v>207011</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -4771,7 +4768,7 @@
         <v>206011</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4779,7 +4776,7 @@
         <v>304012</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -4787,7 +4784,7 @@
         <v>303012</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -4795,7 +4792,7 @@
         <v>303072</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4803,7 +4800,7 @@
         <v>305012</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4811,7 +4808,7 @@
         <v>305072</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4819,7 +4816,7 @@
         <v>303031</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4827,7 +4824,7 @@
         <v>305031</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4835,7 +4832,7 @@
         <v>317012</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4843,7 +4840,7 @@
         <v>320011</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:2">
@@ -4851,7 +4848,7 @@
         <v>207021</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
